--- a/artfynd/S 3856-2024 artfynd.xlsx
+++ b/artfynd/S 3856-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107952031</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103682599</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103683012</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103683109</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103683420</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107905308</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585256</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585261</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1607,6 +1652,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585262</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585263</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585264</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585265</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107903241</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,6 +2176,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107904838</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2210,6 +2285,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>JMN0118</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585227</t>
         </is>
       </c>
     </row>
@@ -2329,6 +2409,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103682829</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2430,6 +2515,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585085</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2531,6 +2621,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585086</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2632,6 +2727,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585047</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2731,6 +2831,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>JMN0118</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585102</t>
         </is>
       </c>
     </row>
@@ -2834,6 +2939,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107952029</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2935,6 +3045,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585209</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3036,6 +3151,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585298</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3137,6 +3257,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585299</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3238,6 +3363,11 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585300</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3349,6 +3479,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7015565</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3455,8 +3590,42 @@
           <t>JMN0118</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585017</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>